--- a/server/master-excel-files/General_BIOLOGY_Grade 6.xlsx
+++ b/server/master-excel-files/General_BIOLOGY_Grade 6.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Downloads\Teachers year plan\BIOLOGY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Desktop\teacher-year-plan-app\server\master-excel-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1056,9 +1056,12 @@
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 E3:G13 H3:I47 J3:K13">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E1:K1 H13:I47 J13:K13 E13:G13">
       <formula1>"Not Started,In Progress,Completed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" errorTitle="Invalid Entry" error="Your entry is not in the list" promptTitle="Select Status" prompt="Please select a status" sqref="E3:K12">
+      <formula1>"Not Assigned,In Progress,Completed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
